--- a/output/INSTRUKCE_usa1_HS_kody.xlsx
+++ b/output/INSTRUKCE_usa1_HS_kody.xlsx
@@ -1561,7 +1561,7 @@
       <c r="H27" s="81" t="n"/>
       <c r="I27" s="102" t="inlineStr">
         <is>
-          <t>3304990000</t>
+          <t>3307900000</t>
         </is>
       </c>
       <c r="K27" s="78" t="n"/>
